--- a/template/templateDataOut.xlsx
+++ b/template/templateDataOut.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="17055"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>流水号</t>
   </si>
   <si>
-    <t>板号</t>
+    <t>厂别区分</t>
+  </si>
+  <si>
+    <t>产线区分</t>
+  </si>
+  <si>
+    <t>材料号</t>
   </si>
   <si>
     <t>捆包号</t>
@@ -41,6 +47,9 @@
     <t>钢种</t>
   </si>
   <si>
+    <t>用途</t>
+  </si>
+  <si>
     <t>长度</t>
   </si>
   <si>
@@ -53,13 +62,28 @@
     <t>检测时间</t>
   </si>
   <si>
-    <t>判级</t>
-  </si>
-  <si>
-    <t>是否合格</t>
+    <t>上表缺陷</t>
+  </si>
+  <si>
+    <t>下表缺陷</t>
   </si>
   <si>
     <t>判级原因</t>
+  </si>
+  <si>
+    <t>产品等级</t>
+  </si>
+  <si>
+    <t>比对等级</t>
+  </si>
+  <si>
+    <t>人工原因</t>
+  </si>
+  <si>
+    <t>比对结果</t>
+  </si>
+  <si>
+    <t>描述</t>
   </si>
 </sst>
 </file>
@@ -741,22 +765,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A:K" totalsRowShown="0">
-  <autoFilter ref="A1:K1048576"/>
-  <tableColumns count="11">
-    <tableColumn id="1" name="流水号"/>
-    <tableColumn id="2" name="板号"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A:S" totalsRowShown="0">
+  <autoFilter ref="A1:S1048576"/>
+  <tableColumns count="19">
+    <tableColumn id="14" name="流水号"/>
+    <tableColumn id="15" name="厂别区分"/>
+    <tableColumn id="1" name="产线区分"/>
+    <tableColumn id="2" name="材料号"/>
     <tableColumn id="3" name="捆包号"/>
     <tableColumn id="4" name="钢种"/>
+    <tableColumn id="19" name="用途"/>
     <tableColumn id="5" name="长度"/>
     <tableColumn id="6" name="宽度"/>
     <tableColumn id="7" name="厚度"/>
     <tableColumn id="8" name="检测时间"/>
-    <tableColumn id="9" name="判级"/>
-    <tableColumn id="10" name="是否合格"/>
-    <tableColumn id="11" name="判级原因"/>
+    <tableColumn id="9" name="上表缺陷"/>
+    <tableColumn id="10" name="下表缺陷"/>
+    <tableColumn id="16" name="判级原因"/>
+    <tableColumn id="18" name="产品等级"/>
+    <tableColumn id="11" name="比对等级"/>
+    <tableColumn id="12" name="人工原因"/>
+    <tableColumn id="13" name="比对结果"/>
+    <tableColumn id="17" name="描述"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1010,10 +1042,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="13" max="13" width="21.75" customWidth="1"/>
+    <col min="14" max="14" width="17.125" customWidth="1"/>
+    <col min="15" max="16" width="11.25" customWidth="1"/>
+    <col min="18" max="18" width="21.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1046,6 +1088,30 @@
       </c>
       <c r="K1" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/template/templateDataOut.xlsx
+++ b/template/templateDataOut.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17055"/>
+    <workbookView windowWidth="32715" windowHeight="16605"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <t>产线区分</t>
   </si>
   <si>
-    <t>材料号</t>
+    <t>钢板号</t>
   </si>
   <si>
     <t>捆包号</t>
@@ -74,16 +74,16 @@
     <t>产品等级</t>
   </si>
   <si>
-    <t>比对等级</t>
+    <t>人工等级</t>
   </si>
   <si>
     <t>人工原因</t>
   </si>
   <si>
-    <t>比对结果</t>
-  </si>
-  <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -765,13 +765,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A:S" totalsRowShown="0">
-  <autoFilter ref="A1:S1048576"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A:R" totalsRowShown="0">
+  <autoFilter ref="A1:R1048576"/>
+  <tableColumns count="18">
     <tableColumn id="14" name="流水号"/>
     <tableColumn id="15" name="厂别区分"/>
     <tableColumn id="1" name="产线区分"/>
-    <tableColumn id="2" name="材料号"/>
+    <tableColumn id="2" name="钢板号"/>
     <tableColumn id="3" name="捆包号"/>
     <tableColumn id="4" name="钢种"/>
     <tableColumn id="19" name="用途"/>
@@ -783,10 +783,9 @@
     <tableColumn id="10" name="下表缺陷"/>
     <tableColumn id="16" name="判级原因"/>
     <tableColumn id="18" name="产品等级"/>
-    <tableColumn id="11" name="比对等级"/>
+    <tableColumn id="11" name="人工等级"/>
     <tableColumn id="12" name="人工原因"/>
-    <tableColumn id="13" name="比对结果"/>
-    <tableColumn id="17" name="描述"/>
+    <tableColumn id="13" name="描述"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1042,7 +1041,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -1052,10 +1051,11 @@
     <col min="13" max="13" width="21.75" customWidth="1"/>
     <col min="14" max="14" width="17.125" customWidth="1"/>
     <col min="15" max="16" width="11.25" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
     <col min="18" max="18" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1110,9 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+    </row>
+    <row r="15" spans="10:10">
+      <c r="J15" t="s">
         <v>18</v>
       </c>
     </row>
